--- a/artfynd/A 43074-2021 artfynd.xlsx
+++ b/artfynd/A 43074-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 43074-2021 artfynd.xlsx
+++ b/artfynd/A 43074-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY150"/>
+  <dimension ref="A1:AZ150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798849</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798852</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798850</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798851</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315730</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798853</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102398678</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1459,6 +1499,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102398681</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1558,6 +1603,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102398702</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1661,6 +1711,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102398765</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1764,6 +1819,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102398960</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1867,6 +1927,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102398991</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1970,6 +2035,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102399031</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2073,6 +2143,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102399211</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2170,6 +2245,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798801</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2285,6 +2365,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97014834</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2382,6 +2467,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798811</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2489,6 +2579,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/164416</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2586,6 +2681,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798785</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2683,6 +2783,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798786</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2780,6 +2885,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798788</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2877,6 +2987,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798789</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2974,6 +3089,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798790</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3071,6 +3191,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798791</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3168,6 +3293,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798796</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3265,6 +3395,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798800</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3362,6 +3497,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798806</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3459,6 +3599,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798810</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3556,6 +3701,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798812</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3653,6 +3803,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798815</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3750,6 +3905,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798817</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3847,6 +4007,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798820</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3944,6 +4109,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798822</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4041,6 +4211,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798824</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4138,6 +4313,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798828</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4235,6 +4415,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798833</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4332,6 +4517,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798843</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4429,6 +4619,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798844</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4526,6 +4721,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798847</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4628,6 +4828,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315717</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4730,6 +4935,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315722</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4832,6 +5042,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315728</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4934,6 +5149,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315729</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5032,6 +5252,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102401023</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5129,6 +5354,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798809</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5226,6 +5456,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798840</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5323,6 +5558,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798835</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5420,6 +5660,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798787</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5517,6 +5762,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798793</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5614,6 +5864,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798803</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5711,6 +5966,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798804</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5808,6 +6068,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798805</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5905,6 +6170,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798821</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6002,6 +6272,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798825</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6099,6 +6374,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798829</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6196,6 +6476,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798832</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6293,6 +6578,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798845</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6390,6 +6680,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798846</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6492,6 +6787,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315716</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6594,6 +6894,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315718</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6696,6 +7001,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315719</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6798,6 +7108,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315721</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6895,6 +7210,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798814</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6992,6 +7312,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798848</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7090,6 +7415,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97156300</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7188,6 +7518,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97155757</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7295,6 +7630,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/932240</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7403,6 +7743,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1042864</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7510,6 +7855,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96857521</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7617,6 +7967,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1043696</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7714,6 +8069,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798826</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7821,6 +8181,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1392902</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7928,6 +8293,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1679328</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8035,6 +8405,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1149227</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8142,6 +8517,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1227219</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8249,6 +8629,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1339421</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8356,6 +8741,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1256526</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8463,6 +8853,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1460114</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8560,6 +8955,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798784</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8657,6 +9057,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798792</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8754,6 +9159,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798831</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8851,6 +9261,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798838</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8953,6 +9368,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105315720</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9060,6 +9480,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1612743</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9167,6 +9592,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2349692</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9274,6 +9704,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1786618</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9371,6 +9806,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798783</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9468,6 +9908,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798795</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9565,6 +10010,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798797</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9662,6 +10112,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798798</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9759,6 +10214,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798799</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9856,6 +10316,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798802</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -9953,6 +10418,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798808</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10050,6 +10520,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798816</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10147,6 +10622,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798818</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10244,6 +10724,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798819</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10341,6 +10826,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798823</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10438,6 +10928,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798830</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -10536,6 +11031,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102403144</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -10638,6 +11138,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312568</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -10740,6 +11245,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105312569</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -10838,6 +11348,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97155656</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -10961,6 +11476,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97015151</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11063,6 +11583,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111823812</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11165,6 +11690,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111823813</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11267,6 +11797,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111823814</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11369,6 +11904,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111823815</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -11471,6 +12011,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111823816</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -11571,6 +12116,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102399422</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -11668,6 +12218,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798813</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -11781,6 +12336,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102541955</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -11900,6 +12460,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99044227</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -11997,6 +12562,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798834</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12094,6 +12664,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798836</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12191,6 +12766,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798837</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12288,6 +12868,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798839</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12385,6 +12970,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798841</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -12482,6 +13072,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798842</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -12585,6 +13180,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102399230</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -12688,6 +13288,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102399243</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -12791,6 +13396,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102399469</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -12894,6 +13504,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102399712</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -12997,6 +13612,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102400033</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13100,6 +13720,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102400071</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13203,6 +13828,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102400079</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13306,6 +13936,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102400091</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -13409,6 +14044,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102400946</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -13512,6 +14152,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102400998</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -13615,6 +14260,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102401287</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -13718,6 +14368,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102401447</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -13821,6 +14476,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102401893</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -13924,6 +14584,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102402040</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14027,6 +14692,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102402139</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14130,6 +14800,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102402225</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14233,6 +14908,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102402334</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14336,6 +15016,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102402415</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -14439,6 +15124,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102402430</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -14542,6 +15232,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102402578</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -14645,6 +15340,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102402705</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -14748,6 +15448,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102402765</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -14851,6 +15556,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102402861</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -14954,6 +15664,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102402956</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15057,6 +15772,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102403074</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15160,6 +15880,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102403102</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15263,6 +15988,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102403118</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15366,6 +16096,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102403165</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -15469,6 +16204,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102402306</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -15571,6 +16311,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97034413</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -15668,8 +16413,164 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96798782</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>